--- a/ApplicationHealthCheckAfterPatch/Config/Applications.xlsx
+++ b/ApplicationHealthCheckAfterPatch/Config/Applications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KARKA-SAAS-DEV\uipath-discussions\ApplicationHealthCheckAfterPatch\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63A4036C-B88D-42B7-8287-40FEBEA0BD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3E412A-3680-4F7E-8426-6E8CB0E8D0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F6976F25-8881-4A74-BADF-7F3ECFBFE83F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F6976F25-8881-4A74-BADF-7F3ECFBFE83F}"/>
   </bookViews>
   <sheets>
     <sheet name="Applications" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>AppID</t>
   </si>
@@ -74,18 +74,12 @@
     <t>Outlook</t>
   </si>
   <si>
-    <t>C:\Program Files\Microsoft Office\root\Office16\OUTLOOK.EXE</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>Delete</t>
   </si>
   <si>
-    <t>outlook-owner@example.com</t>
-  </si>
-  <si>
     <t>APP002</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>teams-owner@example.com</t>
-  </si>
-  <si>
     <t>ScenarioID</t>
   </si>
   <si>
@@ -170,9 +161,6 @@
     <t>Health check attachment test - {token}</t>
   </si>
   <si>
-    <t>C:\HealthCheck\SampleFiles\test-attachment.pdf</t>
-  </si>
-  <si>
     <t>OL-V02</t>
   </si>
   <si>
@@ -182,7 +170,16 @@
     <t>VerifyReceiveAttachment</t>
   </si>
   <si>
-    <t>test-attachment.pdf</t>
+    <t>C:\Program Files\WindowsApps\Microsoft.OutlookForWindows_1.2026.730.100_x64__8wekyb3d8bbwe\olk.exe</t>
+  </si>
+  <si>
+    <t>ramamoorthy.karthikeyan@outlook.com</t>
+  </si>
+  <si>
+    <t>C:\HealthCheck\SampleFiles\MasterReport_214023.html</t>
+  </si>
+  <si>
+    <t>MasterReport_214023.html</t>
   </si>
 </sst>
 </file>
@@ -552,7 +549,7 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -600,10 +597,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -612,24 +609,24 @@
         <v>120</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -638,10 +635,10 @@
         <v>120</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -673,66 +670,66 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
       </c>
       <c r="J2">
         <v>30</v>
@@ -744,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -752,22 +749,22 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>120</v>
@@ -779,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -787,25 +784,25 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J4">
         <v>30</v>
@@ -817,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -825,25 +822,25 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
         <v>46</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>47</v>
       </c>
       <c r="J5">
         <v>120</v>
@@ -855,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N5">
         <v>4</v>
